--- a/AAII_Financials/Yearly/WHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WHG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>WHG</t>
   </si>
@@ -2971,8 +2971,8 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>25400</v>
+        <v>23500</v>
       </c>
       <c r="E60" s="3">
         <v>19800</v>
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10200</v>
+        <v>12100</v>
       </c>
       <c r="E61" s="3">
         <v>3200</v>
